--- a/data/ic_params.xlsx
+++ b/data/ic_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{F84FD8E5-1FFF-4787-86AE-DA4064EEAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE42C3B-AF47-404E-8EFE-3E74FAB6841D}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{F84FD8E5-1FFF-4787-86AE-DA4064EEAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00516055-D582-4DE1-8682-C9DFC7B6177D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{CD76860F-921B-4D74-8C7E-AD0F0543B9C4}"/>
+    <workbookView xWindow="30195" yWindow="1215" windowWidth="21600" windowHeight="12735" xr2:uid="{CD76860F-921B-4D74-8C7E-AD0F0543B9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>raa489300</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>raa489301</t>
   </si>
 </sst>
 </file>
@@ -493,16 +496,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08BF5E0-99D2-4649-8A29-44D221974715}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.140625" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="5" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -519,10 +522,13 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -541,8 +547,11 @@
       <c r="F2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -562,8 +571,11 @@
       <c r="F3">
         <v>29.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -580,10 +592,13 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -602,8 +617,11 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -620,10 +638,13 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -642,8 +663,11 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -660,10 +684,13 @@
         <v>30</v>
       </c>
       <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -680,10 +707,13 @@
         <v>30</v>
       </c>
       <c r="F9">
+        <v>40</v>
+      </c>
+      <c r="G9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -700,10 +730,13 @@
         <v>0.05</v>
       </c>
       <c r="F10">
+        <v>0.05</v>
+      </c>
+      <c r="G10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -720,6 +753,9 @@
         <v>31</v>
       </c>
       <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data/ic_params.xlsx
+++ b/data/ic_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{F84FD8E5-1FFF-4787-86AE-DA4064EEAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00516055-D582-4DE1-8682-C9DFC7B6177D}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{F84FD8E5-1FFF-4787-86AE-DA4064EEAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{362B6328-4E40-264C-A71B-B077153413FA}"/>
   <bookViews>
-    <workbookView xWindow="30195" yWindow="1215" windowWidth="21600" windowHeight="12735" xr2:uid="{CD76860F-921B-4D74-8C7E-AD0F0543B9C4}"/>
+    <workbookView xWindow="46620" yWindow="7820" windowWidth="21600" windowHeight="12740" xr2:uid="{CD76860F-921B-4D74-8C7E-AD0F0543B9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>raa489300</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>raa489301</t>
+  </si>
+  <si>
+    <t>rrb48800</t>
+  </si>
+  <si>
+    <t>QFN5x5</t>
   </si>
 </sst>
 </file>
@@ -197,6 +203,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,16 +506,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08BF5E0-99D2-4649-8A29-44D221974715}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -527,8 +537,11 @@
       <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -550,8 +563,11 @@
       <c r="G2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -574,8 +590,11 @@
       <c r="G3">
         <v>29.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -597,8 +616,11 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -620,8 +642,11 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -643,8 +668,11 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -666,8 +694,11 @@
       <c r="G7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -681,16 +712,19 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -704,16 +738,19 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -735,8 +772,11 @@
       <c r="G10">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -757,6 +797,9 @@
       </c>
       <c r="G11" t="s">
         <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
